--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,27 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126561335</v>
+        <v>126561338</v>
       </c>
       <c r="B3" t="n">
-        <v>56852</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,30 +828,26 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nörder-Långflon, Jmt</t>
+          <t>Spelarberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519438</v>
+        <v>519462</v>
       </c>
       <c r="R3" t="n">
-        <v>6944051</v>
+        <v>6944044</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ej duktig på att flyga, äldre hona?</t>
+          <t>Endast hörd locka, artbestämning något osäker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,27 +918,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126561338</v>
+        <v>126561335</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>56852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,26 +952,30 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spelarberget, Jmt</t>
+          <t>Nörder-Långflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519462</v>
+        <v>519438</v>
       </c>
       <c r="R4" t="n">
-        <v>6944044</v>
+        <v>6944051</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Endast hörd locka, artbestämning något osäker.</t>
+          <t>Ej duktig på att flyga, äldre hona?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1043,251 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127298859</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56852</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spelarberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>519438</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6944048</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127298858</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spelarberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519443</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6943931</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Endast hörd locka, artbestämning något osäker.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Max Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126561338</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56852</v>
+        <v>56856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>127298858</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126561338</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56856</v>
+        <v>56858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>127298858</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126561338</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56858</v>
+        <v>56861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>127298858</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>126561338</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56861</v>
+        <v>56867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>127298858</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56867</v>
+        <v>56852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 103-2025 artfynd.xlsx
+++ b/artfynd/A 103-2025 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>127298859</v>
       </c>
       <c r="B5" t="n">
-        <v>56852</v>
+        <v>56867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
